--- a/final_data_pipeline/output/312140longform_elec_options.xlsx
+++ b/final_data_pipeline/output/312140longform_elec_options.xlsx
@@ -588,7 +588,7 @@
         <v>70</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L2">
         <v>8000</v>
@@ -609,10 +609,10 @@
         <v>4.097340425531915</v>
       </c>
       <c r="R2">
-        <v>1.667307692307692</v>
+        <v>1.722630989917367</v>
       </c>
       <c r="S2">
-        <v>1.799766355140187</v>
+        <v>1.865269081797952</v>
       </c>
       <c r="T2">
         <v>12.15694385248556</v>
@@ -647,7 +647,7 @@
         <v>36</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L3">
         <v>8000</v>
@@ -662,10 +662,10 @@
         <v>253145.1872083376</v>
       </c>
       <c r="R3">
-        <v>1.741590909090909</v>
+        <v>1.803186500133452</v>
       </c>
       <c r="S3">
-        <v>1.89075</v>
+        <v>1.964569140204562</v>
       </c>
       <c r="T3">
         <v>31.6431484010422</v>
@@ -871,7 +871,7 @@
         <v>70</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L7">
         <v>8000</v>
@@ -892,10 +892,10 @@
         <v>4.097340425531915</v>
       </c>
       <c r="R7">
-        <v>1.667307692307692</v>
+        <v>1.722630989917367</v>
       </c>
       <c r="S7">
-        <v>1.799766355140187</v>
+        <v>1.865269081797952</v>
       </c>
       <c r="T7">
         <v>21.68026390753792</v>
@@ -930,7 +930,7 @@
         <v>36</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L8">
         <v>8000</v>
@@ -945,10 +945,10 @@
         <v>451450.1779555182</v>
       </c>
       <c r="R8">
-        <v>1.741590909090909</v>
+        <v>1.803186500133452</v>
       </c>
       <c r="S8">
-        <v>1.89075</v>
+        <v>1.964569140204562</v>
       </c>
       <c r="T8">
         <v>56.43127224443978</v>
@@ -989,7 +989,7 @@
         <v>70</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L9">
         <v>8000</v>
@@ -1010,10 +1010,10 @@
         <v>4.097340425531915</v>
       </c>
       <c r="R9">
-        <v>1.667307692307692</v>
+        <v>1.578134831460674</v>
       </c>
       <c r="S9">
-        <v>1.799766355140187</v>
+        <v>1.695036674816626</v>
       </c>
       <c r="T9">
         <v>14.63523762208856</v>
@@ -1048,7 +1048,7 @@
         <v>36</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L10">
         <v>8000</v>
@@ -1063,10 +1063,10 @@
         <v>304750.9318655474</v>
       </c>
       <c r="R10">
-        <v>1.741590909090909</v>
+        <v>1.642853739876131</v>
       </c>
       <c r="S10">
-        <v>1.89075</v>
+        <v>1.773501823866597</v>
       </c>
       <c r="T10">
         <v>38.09386648319343</v>
@@ -1219,7 +1219,7 @@
         <v>37</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="L13">
         <v>8000</v>
@@ -1266,7 +1266,7 @@
         <v>38</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="L14">
         <v>8000</v>
@@ -1313,7 +1313,7 @@
         <v>38</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="L15">
         <v>8000</v>
@@ -1478,7 +1478,7 @@
         <v>36</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L18">
         <v>8000</v>
@@ -1493,10 +1493,10 @@
         <v>726016.8110556793</v>
       </c>
       <c r="R18">
-        <v>1.741590909090909</v>
+        <v>1.911855479578636</v>
       </c>
       <c r="S18">
-        <v>1.89075</v>
+        <v>2.09608909874769</v>
       </c>
       <c r="T18">
         <v>90.75210138195992</v>
@@ -1531,7 +1531,7 @@
         <v>37</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L19">
         <v>8000</v>
@@ -1584,7 +1584,7 @@
         <v>70</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L20">
         <v>8000</v>
@@ -1605,10 +1605,10 @@
         <v>4.097340425531915</v>
       </c>
       <c r="R20">
-        <v>1.667307692307692</v>
+        <v>1.819666609086197</v>
       </c>
       <c r="S20">
-        <v>1.799766355140187</v>
+        <v>1.981148790245761</v>
       </c>
       <c r="T20">
         <v>34.8659427631173</v>
@@ -1649,7 +1649,7 @@
         <v>70</v>
       </c>
       <c r="K21">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L21">
         <v>8000</v>
@@ -1670,10 +1670,10 @@
         <v>4.097340425531915</v>
       </c>
       <c r="R21">
-        <v>1.667307692307692</v>
+        <v>1.722630989917367</v>
       </c>
       <c r="S21">
-        <v>1.799766355140187</v>
+        <v>1.865269081797952</v>
       </c>
       <c r="T21">
         <v>15.85593813357859</v>
@@ -1708,7 +1708,7 @@
         <v>36</v>
       </c>
       <c r="K22">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L22">
         <v>8000</v>
@@ -1723,10 +1723,10 @@
         <v>330169.6936247601</v>
       </c>
       <c r="R22">
-        <v>1.741590909090909</v>
+        <v>1.803186500133452</v>
       </c>
       <c r="S22">
-        <v>1.89075</v>
+        <v>1.964569140204562</v>
       </c>
       <c r="T22">
         <v>41.27121170309502</v>
@@ -1767,7 +1767,7 @@
         <v>70</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L23">
         <v>8000</v>
@@ -1788,10 +1788,10 @@
         <v>4.097340425531915</v>
       </c>
       <c r="R23">
-        <v>1.667307692307692</v>
+        <v>1.578134831460674</v>
       </c>
       <c r="S23">
-        <v>1.799766355140187</v>
+        <v>1.695036674816626</v>
       </c>
       <c r="T23">
         <v>32.52085163609455</v>
@@ -1826,7 +1826,7 @@
         <v>36</v>
       </c>
       <c r="K24">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L24">
         <v>8000</v>
@@ -1841,10 +1841,10 @@
         <v>677184.7575746218</v>
       </c>
       <c r="R24">
-        <v>1.741590909090909</v>
+        <v>1.642853739876131</v>
       </c>
       <c r="S24">
-        <v>1.89075</v>
+        <v>1.773501823866597</v>
       </c>
       <c r="T24">
         <v>84.64809469682773</v>
@@ -1879,7 +1879,7 @@
         <v>37</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L25">
         <v>8000</v>
